--- a/Data/20240830-20240913_SAU-G0-PL_14天2043次采集.xlsx
+++ b/Data/20240830-20240913_SAU-G0-PL_14天2043次采集.xlsx
@@ -26,10 +26,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy/m/d h:mm:ss"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;/&quot;mm&quot;/&quot;dd&quot; &quot;hh&quot;:&quot;mm&quot;:&quot;ss"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="yyyy&quot;/&quot;mm&quot;/&quot;dd&quot; &quot;hh&quot;:&quot;mm&quot;:&quot;ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -62,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -79,9 +78,6 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -22687,252 +22683,252 @@
       </c>
     </row>
     <row r="2036">
-      <c r="A2036" s="6"/>
+      <c r="A2036" s="2"/>
       <c r="B2036" s="5"/>
       <c r="C2036" s="5"/>
     </row>
     <row r="2037">
-      <c r="A2037" s="6"/>
+      <c r="A2037" s="2"/>
       <c r="B2037" s="5"/>
       <c r="C2037" s="5"/>
     </row>
     <row r="2038">
-      <c r="A2038" s="6"/>
+      <c r="A2038" s="2"/>
       <c r="B2038" s="5"/>
       <c r="C2038" s="5"/>
     </row>
     <row r="2039">
-      <c r="A2039" s="6"/>
+      <c r="A2039" s="2"/>
       <c r="B2039" s="5"/>
       <c r="C2039" s="5"/>
     </row>
     <row r="2040">
-      <c r="A2040" s="6"/>
+      <c r="A2040" s="2"/>
       <c r="B2040" s="5"/>
       <c r="C2040" s="5"/>
     </row>
     <row r="2041">
-      <c r="A2041" s="6"/>
+      <c r="A2041" s="2"/>
       <c r="B2041" s="5"/>
       <c r="C2041" s="5"/>
     </row>
     <row r="2042">
-      <c r="A2042" s="6"/>
+      <c r="A2042" s="2"/>
       <c r="B2042" s="5"/>
       <c r="C2042" s="5"/>
     </row>
     <row r="2043">
-      <c r="A2043" s="6"/>
+      <c r="A2043" s="2"/>
       <c r="B2043" s="5"/>
       <c r="C2043" s="5"/>
     </row>
     <row r="2044">
-      <c r="A2044" s="6"/>
+      <c r="A2044" s="2"/>
       <c r="B2044" s="5"/>
       <c r="C2044" s="5"/>
     </row>
     <row r="2045">
-      <c r="A2045" s="6"/>
+      <c r="A2045" s="2"/>
       <c r="B2045" s="5"/>
       <c r="C2045" s="5"/>
     </row>
     <row r="2046">
-      <c r="A2046" s="6"/>
+      <c r="A2046" s="2"/>
       <c r="B2046" s="5"/>
       <c r="C2046" s="5"/>
     </row>
     <row r="2047">
-      <c r="A2047" s="6"/>
+      <c r="A2047" s="2"/>
       <c r="B2047" s="5"/>
       <c r="C2047" s="5"/>
     </row>
     <row r="2048">
-      <c r="A2048" s="6"/>
+      <c r="A2048" s="2"/>
       <c r="B2048" s="5"/>
       <c r="C2048" s="5"/>
     </row>
     <row r="2049">
-      <c r="A2049" s="6"/>
+      <c r="A2049" s="2"/>
       <c r="B2049" s="5"/>
       <c r="C2049" s="5"/>
     </row>
     <row r="2050">
-      <c r="A2050" s="6"/>
+      <c r="A2050" s="2"/>
       <c r="B2050" s="5"/>
       <c r="C2050" s="5"/>
     </row>
     <row r="2051">
-      <c r="A2051" s="6"/>
+      <c r="A2051" s="2"/>
       <c r="B2051" s="5"/>
       <c r="C2051" s="5"/>
     </row>
     <row r="2052">
-      <c r="A2052" s="6"/>
+      <c r="A2052" s="2"/>
       <c r="B2052" s="5"/>
       <c r="C2052" s="5"/>
     </row>
     <row r="2053">
-      <c r="A2053" s="6"/>
+      <c r="A2053" s="2"/>
       <c r="B2053" s="5"/>
       <c r="C2053" s="5"/>
     </row>
     <row r="2054">
-      <c r="A2054" s="6"/>
+      <c r="A2054" s="2"/>
       <c r="B2054" s="5"/>
       <c r="C2054" s="5"/>
     </row>
     <row r="2055">
-      <c r="A2055" s="6"/>
+      <c r="A2055" s="2"/>
       <c r="B2055" s="5"/>
       <c r="C2055" s="5"/>
     </row>
     <row r="2056">
-      <c r="A2056" s="6"/>
+      <c r="A2056" s="2"/>
       <c r="B2056" s="5"/>
       <c r="C2056" s="5"/>
     </row>
     <row r="2057">
-      <c r="A2057" s="6"/>
+      <c r="A2057" s="2"/>
       <c r="B2057" s="5"/>
       <c r="C2057" s="5"/>
     </row>
     <row r="2058">
-      <c r="A2058" s="6"/>
+      <c r="A2058" s="2"/>
       <c r="B2058" s="5"/>
       <c r="C2058" s="5"/>
     </row>
     <row r="2059">
-      <c r="A2059" s="6"/>
+      <c r="A2059" s="2"/>
       <c r="B2059" s="5"/>
       <c r="C2059" s="5"/>
     </row>
     <row r="2060">
-      <c r="A2060" s="6"/>
+      <c r="A2060" s="2"/>
       <c r="B2060" s="5"/>
       <c r="C2060" s="5"/>
     </row>
     <row r="2061">
-      <c r="A2061" s="6"/>
+      <c r="A2061" s="2"/>
       <c r="B2061" s="5"/>
       <c r="C2061" s="5"/>
     </row>
     <row r="2062">
-      <c r="A2062" s="6"/>
+      <c r="A2062" s="2"/>
       <c r="B2062" s="5"/>
       <c r="C2062" s="5"/>
     </row>
     <row r="2063">
-      <c r="A2063" s="6"/>
+      <c r="A2063" s="2"/>
       <c r="B2063" s="5"/>
       <c r="C2063" s="5"/>
     </row>
     <row r="2064">
-      <c r="A2064" s="6"/>
+      <c r="A2064" s="2"/>
       <c r="B2064" s="5"/>
       <c r="C2064" s="5"/>
     </row>
     <row r="2065">
-      <c r="A2065" s="6"/>
+      <c r="A2065" s="2"/>
       <c r="B2065" s="5"/>
       <c r="C2065" s="5"/>
     </row>
     <row r="2066">
-      <c r="A2066" s="6"/>
+      <c r="A2066" s="2"/>
       <c r="B2066" s="5"/>
       <c r="C2066" s="5"/>
     </row>
     <row r="2067">
-      <c r="A2067" s="6"/>
+      <c r="A2067" s="2"/>
       <c r="B2067" s="5"/>
       <c r="C2067" s="5"/>
     </row>
     <row r="2068">
-      <c r="A2068" s="6"/>
+      <c r="A2068" s="2"/>
       <c r="B2068" s="5"/>
       <c r="C2068" s="5"/>
     </row>
     <row r="2069">
-      <c r="A2069" s="6"/>
+      <c r="A2069" s="2"/>
       <c r="B2069" s="5"/>
       <c r="C2069" s="5"/>
     </row>
     <row r="2070">
-      <c r="A2070" s="6"/>
+      <c r="A2070" s="2"/>
       <c r="B2070" s="5"/>
       <c r="C2070" s="5"/>
     </row>
     <row r="2071">
-      <c r="A2071" s="6"/>
+      <c r="A2071" s="2"/>
       <c r="B2071" s="5"/>
       <c r="C2071" s="5"/>
     </row>
     <row r="2072">
-      <c r="A2072" s="6"/>
+      <c r="A2072" s="2"/>
       <c r="B2072" s="5"/>
       <c r="C2072" s="5"/>
     </row>
     <row r="2073">
-      <c r="A2073" s="6"/>
+      <c r="A2073" s="2"/>
       <c r="B2073" s="5"/>
       <c r="C2073" s="5"/>
     </row>
     <row r="2074">
-      <c r="A2074" s="6"/>
+      <c r="A2074" s="2"/>
       <c r="B2074" s="5"/>
       <c r="C2074" s="5"/>
     </row>
     <row r="2075">
-      <c r="A2075" s="6"/>
+      <c r="A2075" s="2"/>
       <c r="B2075" s="5"/>
       <c r="C2075" s="5"/>
     </row>
     <row r="2076">
-      <c r="A2076" s="6"/>
+      <c r="A2076" s="2"/>
       <c r="B2076" s="5"/>
       <c r="C2076" s="5"/>
     </row>
     <row r="2077">
-      <c r="A2077" s="6"/>
+      <c r="A2077" s="2"/>
       <c r="B2077" s="5"/>
       <c r="C2077" s="5"/>
     </row>
     <row r="2078">
-      <c r="A2078" s="6"/>
+      <c r="A2078" s="2"/>
       <c r="B2078" s="5"/>
       <c r="C2078" s="5"/>
     </row>
     <row r="2079">
-      <c r="A2079" s="6"/>
+      <c r="A2079" s="2"/>
       <c r="B2079" s="5"/>
       <c r="C2079" s="5"/>
     </row>
     <row r="2080">
-      <c r="A2080" s="6"/>
+      <c r="A2080" s="2"/>
       <c r="B2080" s="5"/>
       <c r="C2080" s="5"/>
     </row>
     <row r="2081">
-      <c r="A2081" s="6"/>
+      <c r="A2081" s="2"/>
       <c r="B2081" s="5"/>
       <c r="C2081" s="5"/>
     </row>
     <row r="2082">
-      <c r="A2082" s="6"/>
+      <c r="A2082" s="2"/>
       <c r="B2082" s="5"/>
       <c r="C2082" s="5"/>
     </row>
     <row r="2083">
-      <c r="A2083" s="6"/>
+      <c r="A2083" s="2"/>
       <c r="B2083" s="5"/>
       <c r="C2083" s="5"/>
     </row>
     <row r="2084">
-      <c r="A2084" s="6"/>
+      <c r="A2084" s="2"/>
       <c r="B2084" s="5"/>
       <c r="C2084" s="5"/>
     </row>
     <row r="2085">
-      <c r="A2085" s="6"/>
+      <c r="A2085" s="2"/>
       <c r="B2085" s="5"/>
       <c r="C2085" s="5"/>
     </row>
